--- a/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点20.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点20.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\Tb-云量50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB822923-9541-4BE3-A5C5-F6F7D96EC48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424595E9-B7BD-473D-9191-867D75F9BD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2293,7 +2293,7 @@
         <v>202308</v>
       </c>
       <c r="B95" s="4">
-        <v>90.599917880999996</v>
+        <v>59.927621732299997</v>
       </c>
       <c r="C95">
         <v>15.27</v>
@@ -2313,7 +2313,7 @@
         <v>202309</v>
       </c>
       <c r="B96" s="4">
-        <v>95.841239265599995</v>
+        <v>65.571067898500004</v>
       </c>
       <c r="C96">
         <v>13.159000000000001</v>
@@ -2333,7 +2333,7 @@
         <v>202310</v>
       </c>
       <c r="B97" s="4">
-        <v>93.015905678799996</v>
+        <v>56.412474260899998</v>
       </c>
       <c r="C97">
         <v>1.843</v>
@@ -2353,7 +2353,7 @@
         <v>202311</v>
       </c>
       <c r="B98" s="4">
-        <v>80.892856459399994</v>
+        <v>32.291730114899998</v>
       </c>
       <c r="C98">
         <v>3.532</v>
@@ -2370,7 +2370,7 @@
         <v>202312</v>
       </c>
       <c r="B99" s="4">
-        <v>75.576846915999994</v>
+        <v>26.1328126975</v>
       </c>
       <c r="C99">
         <v>4.1360000000000001</v>
